--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM/BOM_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM/BOM_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{199FC8B5-92EE-42A1-9EA1-97E6BE1E7BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5082AA8E-112C-449A-9186-E44CC0AAF35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{772E28E0-5732-4BD7-952F-F9D4E0A9517A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F12F980-6CBB-4C00-A7D7-F8132859CDFE}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_UZ_PER_loopback_tutorial_ N" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>Designator</t>
   </si>
@@ -197,10 +197,10 @@
     <t>X2</t>
   </si>
   <si>
-    <t>30 Position, Classic PCB Header Strips, 0.100&amp;quot; pitch</t>
-  </si>
-  <si>
-    <t>TSW-115-07-G-D</t>
+    <t>2x15 Pins</t>
+  </si>
+  <si>
+    <t>200-TSW11507GD</t>
   </si>
   <si>
     <t>TSW-115-XX-YY-D</t>
@@ -611,7 +611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E509B4CD-60AC-4B2D-980C-2BDAC77E07D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D211519-B064-40A9-811E-023EEA06DC87}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -837,10 +837,12 @@
       <c r="B8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>54</v>
@@ -848,7 +850,9 @@
       <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="H8" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>

--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM/BOM_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM/BOM_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5082AA8E-112C-449A-9186-E44CC0AAF35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{133567D5-129B-4B6B-8959-7DF2C7F506B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F12F980-6CBB-4C00-A7D7-F8132859CDFE}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{362819B9-CF51-4E4B-8819-E77123F198CE}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_UZ_PER_loopback_tutorial_ N" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>SMD resistor 0.1%, SMD resistor 0.1%, 10ppm, SMD resistor 1%, SMD resistor E24 series</t>
   </si>
   <si>
-    <t>66-PCFW0603LF031001B, 279-RQ73C1J10KBTD, 71-CRCW0603-24.9K-E3 , 660-RK73B1JTTD222J, 660-RK73B1JTTD432J</t>
+    <t>66-PCFW0603LF031001B, 279-RQ73C1J10KBTD, 71-CRCW0603-24.9K-E3 , 660-RK73B1JTTD103J, 660-RK73B1JTTD432J</t>
   </si>
   <si>
     <t>[NoValue], =LCSC Part Number</t>
@@ -143,7 +143,7 @@
     <t>[NoValue], LCSC</t>
   </si>
   <si>
-    <t>1k, 10k, 24k9, 2k2, 4k3</t>
+    <t>1k, 10k, 24k9, 4k3</t>
   </si>
   <si>
     <t>Serial1</t>
@@ -611,7 +611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D211519-B064-40A9-811E-023EEA06DC87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD44101-3D92-4E30-83E4-D166DB9CA6FF}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM/BOM_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM/BOM_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{133567D5-129B-4B6B-8959-7DF2C7F506B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C7B92F7-03A5-42E1-9534-4C9296716B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{362819B9-CF51-4E4B-8819-E77123F198CE}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDA413A0-2B5A-4007-9C00-11665A9DBA4F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_UZ_PER_loopback_tutorial_ N" sheetId="1" r:id="rId1"/>
@@ -74,148 +74,148 @@
     <t>D0, D1, D2, D3, D4, D5, D6</t>
   </si>
   <si>
-    <t>WL-SMCW SMD Mono-color Chip LED Waterclear Blue, WL-SMCW SMD Mono-color Chip LED Waterclear Green, WL-SMCW SMD Mono-color Chip LED Waterclear Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710-150060BS84000, 710-150060GS84000, 710-150060RS86000 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3408611 , 3408612 , 3408608 </t>
+    <t>Standard LEDs - SMD 0603 blue, Standard LEDs - SMD 0603 green, Standard LEDs - SMD 0603 red</t>
+  </si>
+  <si>
+    <t>=LCSC Part Number</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>=Value</t>
+  </si>
+  <si>
+    <t>WL-SMCW_0603</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>LED Blue, LED Green, LED Red</t>
+  </si>
+  <si>
+    <t>LPF0_C1, LPF0_C2, LPF1_C1, LPF1_C2, LPF2_C1, LPF2_C2, LPF3_C1, LPF3_C2, LPF4_C1, LPF4_C2, LPF5_C1, LPF5_C2</t>
+  </si>
+  <si>
+    <t>50V 1uF X7R ±10% 0603 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS, Capacitor 0603, 50 VDC, 100nF, X7R</t>
+  </si>
+  <si>
+    <t>=LCSC Part Number, 80-C603C104K5RAC3121</t>
+  </si>
+  <si>
+    <t>963-UMK107AB7105MA-T, =LCSC Part Number</t>
+  </si>
+  <si>
+    <t>C_0603</t>
+  </si>
+  <si>
+    <t>LCSC, Mouser</t>
+  </si>
+  <si>
+    <t>Mouser, LCSC</t>
+  </si>
+  <si>
+    <t>1 µF, 100 nF</t>
+  </si>
+  <si>
+    <t>LPF0_R1, LPF0_R2, LPF1_R1, LPF1_R2, LPF2_R1, LPF2_R2, LPF3_R1, LPF3_R2, LPF4_R1, LPF4_R2, LPF5_R1, LPF5_R2, R0, R0b, R3, R3b, R4, R5, R5b, R6, R7, R7b, R8, R9, R9b, R10, R11, R11b, R12, R13, R13b, R14</t>
+  </si>
+  <si>
+    <t>SMD resistor 0.1%, SMD resistor 0.1%, 10ppm, SMD resistor E24 series</t>
+  </si>
+  <si>
+    <t>66-PCFW0603LF031001B, 279-RQ73C1J10KBTD, 660-RK73B1JTTD433J</t>
+  </si>
+  <si>
+    <t>[NoValue], =LCSC Part Number</t>
+  </si>
+  <si>
+    <t>RES 0603_1608</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>[NoValue], LCSC</t>
+  </si>
+  <si>
+    <t>1k, 10k, 43k</t>
+  </si>
+  <si>
+    <t>Serial1</t>
+  </si>
+  <si>
+    <t>Field to put in a serial number</t>
+  </si>
+  <si>
+    <t>Serial #</t>
+  </si>
+  <si>
+    <t>SERIAL</t>
+  </si>
+  <si>
+    <t>T1, T2, T3, T4, T5, T6</t>
+  </si>
+  <si>
+    <t>Bipolartransistor, 40V 200mW 200mA 100@10mA,1V 300MHz 300mV@50mA,5mA NPN +150℃@(Tj) SOT-23(SOT-23-3)</t>
+  </si>
+  <si>
+    <t>MMBT3904</t>
   </si>
   <si>
     <t>=Manufacturer Part Number</t>
   </si>
   <si>
-    <t>WL-SMCW_0603</t>
-  </si>
-  <si>
-    <t>Mouser</t>
+    <t>SOT95P280X145-3N</t>
+  </si>
+  <si>
+    <t>LCSC/JLCPCB</t>
+  </si>
+  <si>
+    <t>40 V</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>2.54 mm Double Row Terminal Assembly</t>
+  </si>
+  <si>
+    <t>IPL1-115-01-L-D-K</t>
+  </si>
+  <si>
+    <t>IPL1-115-01-YYY-D-K</t>
+  </si>
+  <si>
+    <t>Samtec</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>2x15 Pins</t>
+  </si>
+  <si>
+    <t>200-TSW11507GD</t>
+  </si>
+  <si>
+    <t>TSW-115-XX-YY-D</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>CAT5, RJ45 Connector, 1x2</t>
+  </si>
+  <si>
+    <t>1860605</t>
+  </si>
+  <si>
+    <t>RJHSE-5380-02</t>
   </si>
   <si>
     <t>Farnell</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>LPF0_C1, LPF0_C2, LPF1_C1, LPF1_C2, LPF2_C1, LPF2_C2, LPF3_C1, LPF3_C2, LPF4_C1, LPF4_C2, LPF5_C1, LPF5_C2</t>
-  </si>
-  <si>
-    <t>50V 1uF X7R ±10% 0603 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS, Capacitor 0603, 50 VDC, 100nF, X7R</t>
-  </si>
-  <si>
-    <t>=LCSC Part Number, 80-C603C104K5RAC3121</t>
-  </si>
-  <si>
-    <t>963-UMK107AB7105MA-T, =LCSC Part Number</t>
-  </si>
-  <si>
-    <t>=Value</t>
-  </si>
-  <si>
-    <t>C_0603</t>
-  </si>
-  <si>
-    <t>LCSC, Mouser</t>
-  </si>
-  <si>
-    <t>Mouser, LCSC</t>
-  </si>
-  <si>
-    <t>1 µF, 100 nF</t>
-  </si>
-  <si>
-    <t>LPF0_R1, LPF0_R2, LPF1_R1, LPF1_R2, LPF2_R1, LPF2_R2, LPF3_R1, LPF3_R2, LPF4_R1, LPF4_R2, LPF5_R1, LPF5_R2, R0, R3, R4, R5, R6, R7, R8, R9, R10, R11, R12, R13, R14</t>
-  </si>
-  <si>
-    <t>SMD resistor 0.1%, SMD resistor 0.1%, 10ppm, SMD resistor 1%, SMD resistor E24 series</t>
-  </si>
-  <si>
-    <t>66-PCFW0603LF031001B, 279-RQ73C1J10KBTD, 71-CRCW0603-24.9K-E3 , 660-RK73B1JTTD103J, 660-RK73B1JTTD432J</t>
-  </si>
-  <si>
-    <t>[NoValue], =LCSC Part Number</t>
-  </si>
-  <si>
-    <t>RES 0603_1608</t>
-  </si>
-  <si>
-    <t>[NoValue], LCSC</t>
-  </si>
-  <si>
-    <t>1k, 10k, 24k9, 4k3</t>
-  </si>
-  <si>
-    <t>Serial1</t>
-  </si>
-  <si>
-    <t>Field to put in a serial number</t>
-  </si>
-  <si>
-    <t>Serial #</t>
-  </si>
-  <si>
-    <t>SERIAL</t>
-  </si>
-  <si>
-    <t>T1, T2, T3, T4, T5, T6</t>
-  </si>
-  <si>
-    <t>Bipolartransistor, 40V 200mW 200mA 100@10mA,1V 300MHz 300mV@50mA,5mA NPN +150℃@(Tj) SOT-23(SOT-23-3)</t>
-  </si>
-  <si>
-    <t>MMBT3904</t>
-  </si>
-  <si>
-    <t>=LCSC Part Number</t>
-  </si>
-  <si>
-    <t>SOT95P280X145-3N</t>
-  </si>
-  <si>
-    <t>LCSC/JLCPCB</t>
-  </si>
-  <si>
-    <t>40 V</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>2.54 mm Double Row Terminal Assembly</t>
-  </si>
-  <si>
-    <t>IPL1-115-01-L-D-K</t>
-  </si>
-  <si>
-    <t>IPL1-115-01-YYY-D-K</t>
-  </si>
-  <si>
-    <t>Samtec</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>2x15 Pins</t>
-  </si>
-  <si>
-    <t>200-TSW11507GD</t>
-  </si>
-  <si>
-    <t>TSW-115-XX-YY-D</t>
-  </si>
-  <si>
-    <t>X3</t>
-  </si>
-  <si>
-    <t>CAT5, RJ45 Connector, 1x2</t>
-  </si>
-  <si>
-    <t>1860605</t>
-  </si>
-  <si>
-    <t>RJHSE-5380-02</t>
   </si>
 </sst>
 </file>
@@ -611,7 +611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD44101-3D92-4E30-83E4-D166DB9CA6FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787223AA-7818-42C9-89A9-80BF73BE886F}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -680,90 +680,90 @@
         <v>16</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G3" s="1">
         <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="1">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -774,110 +774,110 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="G6" s="1">
         <v>6</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
